--- a/7 semester/SMAD/lab3/Vanus/lab3.xlsx
+++ b/7 semester/SMAD/lab3/Vanus/lab3.xlsx
@@ -1,15 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24332"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sasha\BSUIR\7 semester\SMAD\lab3\Vanus\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB45930F-F610-45A9-8ECC-9EF760A7946F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="10755"/>
+    <workbookView xWindow="46665" yWindow="1110" windowWidth="28800" windowHeight="16545" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -130,15 +147,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="0.0000"/>
-    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="2">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -152,353 +165,16 @@
       <name val="Menlo"/>
       <charset val="134"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Aptos Narrow"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Aptos Narrow"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Aptos Narrow"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Aptos Narrow"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="13">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -560,253 +236,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -817,92 +251,51 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="60% - Accent6" xfId="1" builtinId="52"/>
-    <cellStyle name="40% - Accent6" xfId="2" builtinId="51"/>
-    <cellStyle name="60% - Accent5" xfId="3" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="4" builtinId="49"/>
-    <cellStyle name="40% - Accent5" xfId="5" builtinId="47"/>
-    <cellStyle name="20% - Accent5" xfId="6" builtinId="46"/>
-    <cellStyle name="60% - Accent4" xfId="7" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="8" builtinId="45"/>
-    <cellStyle name="40% - Accent4" xfId="9" builtinId="43"/>
-    <cellStyle name="Accent4" xfId="10" builtinId="41"/>
-    <cellStyle name="Linked Cell" xfId="11" builtinId="24"/>
-    <cellStyle name="40% - Accent3" xfId="12" builtinId="39"/>
-    <cellStyle name="60% - Accent2" xfId="13" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="14" builtinId="37"/>
-    <cellStyle name="40% - Accent2" xfId="15" builtinId="35"/>
-    <cellStyle name="20% - Accent2" xfId="16" builtinId="34"/>
-    <cellStyle name="Accent2" xfId="17" builtinId="33"/>
-    <cellStyle name="40% - Accent1" xfId="18" builtinId="31"/>
-    <cellStyle name="20% - Accent1" xfId="19" builtinId="30"/>
-    <cellStyle name="Accent1" xfId="20" builtinId="29"/>
-    <cellStyle name="Neutral" xfId="21" builtinId="28"/>
-    <cellStyle name="60% - Accent1" xfId="22" builtinId="32"/>
-    <cellStyle name="Bad" xfId="23" builtinId="27"/>
-    <cellStyle name="20% - Accent4" xfId="24" builtinId="42"/>
-    <cellStyle name="Total" xfId="25" builtinId="25"/>
-    <cellStyle name="Output" xfId="26" builtinId="21"/>
-    <cellStyle name="Currency" xfId="27" builtinId="4"/>
-    <cellStyle name="20% - Accent3" xfId="28" builtinId="38"/>
-    <cellStyle name="Note" xfId="29" builtinId="10"/>
-    <cellStyle name="Input" xfId="30" builtinId="20"/>
-    <cellStyle name="Heading 4" xfId="31" builtinId="19"/>
-    <cellStyle name="Calculation" xfId="32" builtinId="22"/>
-    <cellStyle name="Good" xfId="33" builtinId="26"/>
-    <cellStyle name="Heading 3" xfId="34" builtinId="18"/>
-    <cellStyle name="CExplanatory Text" xfId="35" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="36" builtinId="16"/>
-    <cellStyle name="Comma [0]" xfId="37" builtinId="6"/>
-    <cellStyle name="20% - Accent6" xfId="38" builtinId="50"/>
-    <cellStyle name="Title" xfId="39" builtinId="15"/>
-    <cellStyle name="Currency [0]" xfId="40" builtinId="7"/>
-    <cellStyle name="Warning Text" xfId="41" builtinId="11"/>
-    <cellStyle name="Followed Hyperlink" xfId="42" builtinId="9"/>
-    <cellStyle name="Heading 2" xfId="43" builtinId="17"/>
-    <cellStyle name="Comma" xfId="44" builtinId="3"/>
-    <cellStyle name="Check Cell" xfId="45" builtinId="23"/>
-    <cellStyle name="60% - Accent3" xfId="46" builtinId="40"/>
-    <cellStyle name="Percent" xfId="47" builtinId="5"/>
-    <cellStyle name="Hyperlink" xfId="48" builtinId="8"/>
+  <cellStyles count="1">
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="zh-CN"/>
+  <c:lang val="ru-RU"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -917,7 +310,7 @@
     <c:plotArea>
       <c:layout/>
       <c:scatterChart>
-        <c:scatterStyle val="marker"/>
+        <c:scatterStyle val="lineMarker"/>
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
@@ -944,9 +337,6 @@
               <a:effectLst/>
             </c:spPr>
           </c:marker>
-          <c:dLbls>
-            <c:delete val="1"/>
-          </c:dLbls>
           <c:xVal>
             <c:numRef>
               <c:f>Лист1!$B$2:$B$21</c:f>
@@ -1086,6 +476,11 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-EC68-4D9E-BE6D-E26306BF7041}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
@@ -1155,6 +550,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1980130255"/>
@@ -1218,6 +614,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1980128543"/>
@@ -1258,6 +655,7 @@
       <a:pPr>
         <a:defRPr lang="en-US"/>
       </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -1269,9 +667,9 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="zh-CN"/>
+  <c:lang val="ru-RU"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1321,7 +719,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1330,6 +727,26 @@
         </a:ln>
         <a:effectLst/>
       </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
@@ -1341,15 +758,7 @@
           <c:idx val="1"/>
           <c:order val="0"/>
           <c:tx>
-            <c:strRef>
-              <c:f>"ŷпр"</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>ŷпр</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+            <c:v>ŷпр</c:v>
           </c:tx>
           <c:spPr>
             <a:ln w="28575" cap="rnd">
@@ -1363,9 +772,6 @@
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
-          <c:dLbls>
-            <c:delete val="1"/>
-          </c:dLbls>
           <c:cat>
             <c:numRef>
               <c:f>Лист1!$A$63:$A$71</c:f>
@@ -1409,50 +815,47 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>216.647267880942</c:v>
+                  <c:v>216.64726788094183</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>224.725899600178</c:v>
+                  <c:v>224.72589960017771</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>232.804531319414</c:v>
+                  <c:v>232.80453131941363</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>240.88316303865</c:v>
+                  <c:v>240.88316303864951</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>248.961794757885</c:v>
+                  <c:v>248.9617947578854</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>257.040426477121</c:v>
+                  <c:v>257.04042647712129</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>265.119058196357</c:v>
+                  <c:v>265.11905819635717</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>273.197689915593</c:v>
+                  <c:v>273.19768991559306</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>281.276321634829</c:v>
+                  <c:v>281.27632163482895</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-171F-4232-B183-9A85BB153C4C}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="2"/>
           <c:order val="1"/>
           <c:tx>
-            <c:strRef>
-              <c:f>"лев.дов.инт."</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>лев.дов.инт.</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+            <c:v>лев.дов.инт.</c:v>
           </c:tx>
           <c:spPr>
             <a:ln w="28575" cap="rnd">
@@ -1466,9 +869,6 @@
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
-          <c:dLbls>
-            <c:delete val="1"/>
-          </c:dLbls>
           <c:cat>
             <c:numRef>
               <c:f>Лист1!$A$63:$A$71</c:f>
@@ -1512,50 +912,47 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>210.212241778178</c:v>
+                  <c:v>210.21224177817754</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>219.449289483242</c:v>
+                  <c:v>219.4492894832417</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>228.523701666166</c:v>
+                  <c:v>228.52370166616632</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>237.297326242981</c:v>
+                  <c:v>237.29732624298131</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>245.579372054956</c:v>
+                  <c:v>245.57937205495614</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>253.289003284719</c:v>
+                  <c:v>253.28900328471937</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>260.563248344446</c:v>
+                  <c:v>260.56324834444638</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>267.586320594641</c:v>
+                  <c:v>267.58632059464117</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>274.474162954193</c:v>
+                  <c:v>274.4741629541931</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-171F-4232-B183-9A85BB153C4C}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="3"/>
           <c:order val="2"/>
           <c:tx>
-            <c:strRef>
-              <c:f>"прав.дов.инт."</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>прав.дов.инт.</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+            <c:v>прав.дов.инт.</c:v>
           </c:tx>
           <c:spPr>
             <a:ln w="28575" cap="rnd">
@@ -1569,9 +966,6 @@
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
-          <c:dLbls>
-            <c:delete val="1"/>
-          </c:dLbls>
           <c:cat>
             <c:numRef>
               <c:f>Лист1!$A$63:$A$71</c:f>
@@ -1615,36 +1009,41 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>223.082293983706</c:v>
+                  <c:v>223.08229398370611</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>230.002509717114</c:v>
+                  <c:v>230.00250971711372</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>237.085360972661</c:v>
+                  <c:v>237.08536097266094</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>244.468999834318</c:v>
+                  <c:v>244.46899983431771</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>252.344217460815</c:v>
+                  <c:v>252.34421746081466</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>260.791849669523</c:v>
+                  <c:v>260.79184966952323</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>269.674868048268</c:v>
+                  <c:v>269.67486804826797</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>278.809059236545</c:v>
+                  <c:v>278.80905923654495</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>288.078480315465</c:v>
+                  <c:v>288.07848031546479</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-171F-4232-B183-9A85BB153C4C}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
@@ -1654,7 +1053,6 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:marker val="0"/>
         <c:smooth val="0"/>
         <c:axId val="291893408"/>
         <c:axId val="292084016"/>
@@ -1700,6 +1098,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="292084016"/>
@@ -1760,6 +1159,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="291893408"/>
@@ -1776,7 +1176,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1802,6 +1201,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
         </a:p>
       </c:txPr>
     </c:legend>
@@ -1831,6 +1231,7 @@
       <a:pPr>
         <a:defRPr lang="en-US"/>
       </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -1842,9 +1243,9 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="zh-CN"/>
+  <c:lang val="ru-RU"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1894,7 +1295,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1903,6 +1303,26 @@
         </a:ln>
         <a:effectLst/>
       </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
@@ -1914,15 +1334,7 @@
           <c:idx val="1"/>
           <c:order val="0"/>
           <c:tx>
-            <c:strRef>
-              <c:f>"ŷпр"</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>ŷпр</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+            <c:v>ŷпр</c:v>
           </c:tx>
           <c:spPr>
             <a:ln w="28575" cap="rnd">
@@ -1936,9 +1348,6 @@
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
-          <c:dLbls>
-            <c:delete val="1"/>
-          </c:dLbls>
           <c:cat>
             <c:numRef>
               <c:f>Лист1!$A$63:$A$71</c:f>
@@ -1982,50 +1391,47 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>216.647267880942</c:v>
+                  <c:v>216.64726788094183</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>224.725899600178</c:v>
+                  <c:v>224.72589960017771</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>232.804531319414</c:v>
+                  <c:v>232.80453131941363</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>240.88316303865</c:v>
+                  <c:v>240.88316303864951</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>248.961794757885</c:v>
+                  <c:v>248.9617947578854</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>257.040426477121</c:v>
+                  <c:v>257.04042647712129</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>265.119058196357</c:v>
+                  <c:v>265.11905819635717</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>273.197689915593</c:v>
+                  <c:v>273.19768991559306</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>281.276321634829</c:v>
+                  <c:v>281.27632163482895</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-D123-4611-BEB9-2C0DE16A3D20}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="2"/>
           <c:order val="1"/>
           <c:tx>
-            <c:strRef>
-              <c:f>"лев.дов.инт."</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>лев.дов.инт.</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+            <c:v>лев.дов.инт.</c:v>
           </c:tx>
           <c:spPr>
             <a:ln w="28575" cap="rnd">
@@ -2039,9 +1445,6 @@
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
-          <c:dLbls>
-            <c:delete val="1"/>
-          </c:dLbls>
           <c:cat>
             <c:numRef>
               <c:f>Лист1!$A$63:$A$71</c:f>
@@ -2085,50 +1488,47 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>208.850847889639</c:v>
+                  <c:v>208.85084788963886</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>218.332970038584</c:v>
+                  <c:v>218.33297003858365</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>227.618049500233</c:v>
+                  <c:v>227.61804950023298</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>236.538706740751</c:v>
+                  <c:v>236.53870674075074</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>244.863786830796</c:v>
+                  <c:v>244.8637868307961</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>252.495352330411</c:v>
+                  <c:v>252.49535233041098</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>259.599421377673</c:v>
+                  <c:v>259.59942137767291</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>266.399179504942</c:v>
+                  <c:v>266.39917950494214</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>273.035098510817</c:v>
+                  <c:v>273.03509851081657</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-D123-4611-BEB9-2C0DE16A3D20}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="3"/>
           <c:order val="2"/>
           <c:tx>
-            <c:strRef>
-              <c:f>"прав.дов.инт."</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>прав.дов.инт.</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+            <c:v>прав.дов.инт.</c:v>
           </c:tx>
           <c:spPr>
             <a:ln w="28575" cap="rnd">
@@ -2142,9 +1542,6 @@
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
-          <c:dLbls>
-            <c:delete val="1"/>
-          </c:dLbls>
           <c:cat>
             <c:numRef>
               <c:f>Лист1!$A$63:$A$71</c:f>
@@ -2188,36 +1585,41 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>224.443687872245</c:v>
+                  <c:v>224.44368787224479</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>231.118829161772</c:v>
+                  <c:v>231.11882916177177</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>237.991013138594</c:v>
+                  <c:v>237.99101313859427</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>245.227619336548</c:v>
+                  <c:v>245.22761933654829</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>253.059802684975</c:v>
+                  <c:v>253.0598026849747</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>261.585500623832</c:v>
+                  <c:v>261.58550062383159</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>270.638695015041</c:v>
+                  <c:v>270.63869501504143</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>279.996200326244</c:v>
+                  <c:v>279.99620032624398</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>289.517544758841</c:v>
+                  <c:v>289.51754475884132</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-D123-4611-BEB9-2C0DE16A3D20}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
@@ -2227,7 +1629,6 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:marker val="0"/>
         <c:smooth val="0"/>
         <c:axId val="291893408"/>
         <c:axId val="292084016"/>
@@ -2273,6 +1674,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="292084016"/>
@@ -2333,6 +1735,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="291893408"/>
@@ -2349,7 +1752,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -2375,6 +1777,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
         </a:p>
       </c:txPr>
     </c:legend>
@@ -2404,6 +1807,7 @@
       <a:pPr>
         <a:defRPr lang="en-US"/>
       </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -2415,9 +1819,9 @@
 </file>
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="zh-CN"/>
+  <c:lang val="ru-RU"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2467,7 +1871,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -2476,6 +1879,26 @@
         </a:ln>
         <a:effectLst/>
       </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
@@ -2487,15 +1910,7 @@
           <c:idx val="1"/>
           <c:order val="0"/>
           <c:tx>
-            <c:strRef>
-              <c:f>"ŷпр"</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>ŷпр</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+            <c:v>ŷпр</c:v>
           </c:tx>
           <c:spPr>
             <a:ln w="28575" cap="rnd">
@@ -2509,9 +1924,6 @@
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
-          <c:dLbls>
-            <c:delete val="1"/>
-          </c:dLbls>
           <c:cat>
             <c:numRef>
               <c:f>Лист1!$A$63:$A$71</c:f>
@@ -2555,50 +1967,47 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>216.647267880942</c:v>
+                  <c:v>216.64726788094183</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>224.725899600178</c:v>
+                  <c:v>224.72589960017771</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>232.804531319414</c:v>
+                  <c:v>232.80453131941363</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>240.88316303865</c:v>
+                  <c:v>240.88316303864951</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>248.961794757885</c:v>
+                  <c:v>248.9617947578854</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>257.040426477121</c:v>
+                  <c:v>257.04042647712129</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>265.119058196357</c:v>
+                  <c:v>265.11905819635717</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>273.197689915593</c:v>
+                  <c:v>273.19768991559306</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>281.276321634829</c:v>
+                  <c:v>281.27632163482895</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-BF29-4586-AAB8-5AF842E26966}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="2"/>
           <c:order val="1"/>
           <c:tx>
-            <c:strRef>
-              <c:f>"лев.дов.инт."</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>лев.дов.инт.</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+            <c:v>лев.дов.инт.</c:v>
           </c:tx>
           <c:spPr>
             <a:ln w="28575" cap="rnd">
@@ -2612,9 +2021,6 @@
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
-          <c:dLbls>
-            <c:delete val="1"/>
-          </c:dLbls>
           <c:cat>
             <c:numRef>
               <c:f>Лист1!$A$63:$A$71</c:f>
@@ -2658,50 +2064,47 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>205.965514624234</c:v>
+                  <c:v>205.96551462423358</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>215.9670466599</c:v>
+                  <c:v>215.96704665990001</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>225.69861358734</c:v>
+                  <c:v>225.69861358734028</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>234.93089132157</c:v>
+                  <c:v>234.93089132156987</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>243.34717810434</c:v>
+                  <c:v>243.3471781043402</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>250.813291378863</c:v>
+                  <c:v>250.81329137886325</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>257.556690003058</c:v>
+                  <c:v>257.55669000305846</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>263.883156988847</c:v>
+                  <c:v>263.88315698884662</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>269.985150553438</c:v>
+                  <c:v>269.98515055343796</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-BF29-4586-AAB8-5AF842E26966}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="3"/>
           <c:order val="2"/>
           <c:tx>
-            <c:strRef>
-              <c:f>"прав.дов.инт."</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>прав.дов.инт.</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+            <c:v>прав.дов.инт.</c:v>
           </c:tx>
           <c:spPr>
             <a:ln w="28575" cap="rnd">
@@ -2715,9 +2118,6 @@
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
-          <c:dLbls>
-            <c:delete val="1"/>
-          </c:dLbls>
           <c:cat>
             <c:numRef>
               <c:f>Лист1!$A$63:$A$71</c:f>
@@ -2761,36 +2161,41 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>227.32902113765</c:v>
+                  <c:v>227.32902113765007</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>233.484752540455</c:v>
+                  <c:v>233.48475254045542</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>239.910449051487</c:v>
+                  <c:v>239.91044905148698</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>246.835434755729</c:v>
+                  <c:v>246.83543475572915</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>254.576411411431</c:v>
+                  <c:v>254.5764114114306</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>263.267561575379</c:v>
+                  <c:v>263.26756157537932</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>272.681426389656</c:v>
+                  <c:v>272.68142638965588</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>282.512222842339</c:v>
+                  <c:v>282.5122228423395</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>292.56749271622</c:v>
+                  <c:v>292.56749271621993</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-BF29-4586-AAB8-5AF842E26966}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
@@ -2800,7 +2205,6 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:marker val="0"/>
         <c:smooth val="0"/>
         <c:axId val="291893408"/>
         <c:axId val="292084016"/>
@@ -2846,6 +2250,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="292084016"/>
@@ -2906,6 +2311,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="291893408"/>
@@ -2922,7 +2328,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -2948,6 +2353,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
         </a:p>
       </c:txPr>
     </c:legend>
@@ -2977,6 +2383,7 @@
       <a:pPr>
         <a:defRPr lang="en-US"/>
       </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -2988,9 +2395,9 @@
 </file>
 
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="zh-CN"/>
+  <c:lang val="ru-RU"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -3024,11 +2431,9 @@
               <a:rPr lang="ru-RU"/>
               <a:t>график ошибки</a:t>
             </a:r>
-            <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -3037,26 +2442,38 @@
         </a:ln>
         <a:effectLst/>
       </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
       <c:scatterChart>
-        <c:scatterStyle val="marker"/>
+        <c:scatterStyle val="lineMarker"/>
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
-            <c:strRef>
-              <c:f>"ошибки"</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>ошибки</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+            <c:v>ошибки</c:v>
           </c:tx>
           <c:spPr>
             <a:ln w="25400" cap="rnd">
@@ -3080,9 +2497,6 @@
               <a:effectLst/>
             </c:spPr>
           </c:marker>
-          <c:dLbls>
-            <c:delete val="1"/>
-          </c:dLbls>
           <c:xVal>
             <c:numRef>
               <c:f>Лист1!$B$2:$B$21</c:f>
@@ -3159,69 +2573,74 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="20"/>
                 <c:pt idx="0">
-                  <c:v>-10.8045313194136</c:v>
+                  <c:v>-10.804531319413627</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>-7.9617947578854</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-14.0404264771213</c:v>
+                  <c:v>-14.040426477121287</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>11.8023100844069</c:v>
+                  <c:v>11.80231008440694</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-12.1190581963572</c:v>
+                  <c:v>-12.119058196357173</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>6.11683696135049</c:v>
+                  <c:v>6.1168369613504865</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>13.1954686805864</c:v>
+                  <c:v>13.195468680586373</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>10.8809418036428</c:v>
+                  <c:v>10.880941803642827</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3.95957352287871</c:v>
+                  <c:v>3.9595735228787134</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>13.1168369613505</c:v>
+                  <c:v>13.116836961350486</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>4.27410039982229</c:v>
+                  <c:v>4.274100399822288</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.0382052421146</c:v>
+                  <c:v>3.8205242114599969E-2</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-5.04042647712129</c:v>
+                  <c:v>-5.0404264771212866</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>5.80231008440694</c:v>
+                  <c:v>5.8023100844069404</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-3.11905819635717</c:v>
+                  <c:v>-3.1190581963571731</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-6.27632163482895</c:v>
+                  <c:v>-6.2763216348289461</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-5.64726788094183</c:v>
+                  <c:v>-5.6472678809418255</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-4.72589960017771</c:v>
+                  <c:v>-4.725899600177712</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1.35273211905817</c:v>
+                  <c:v>1.3527321190581745</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>-0.804531319413627</c:v>
+                  <c:v>-0.80453131941362699</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-9789-45B3-A658-11AACE11159F}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
@@ -3289,6 +2708,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1658768272"/>
@@ -3350,6 +2770,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1658524432"/>
@@ -3390,6 +2811,7 @@
       <a:pPr>
         <a:defRPr lang="en-US"/>
       </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -6181,7 +5603,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>14</xdr:col>
@@ -6195,14 +5617,20 @@
       <xdr:row>16</xdr:row>
       <xdr:rowOff>16934</xdr:rowOff>
     </xdr:to>
-    <xdr:graphicFrame>
+    <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Диаграмма 1"/>
+        <xdr:cNvPr id="2" name="Диаграмма 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="16339820" y="607695"/>
-        <a:ext cx="6327775" cy="2885440"/>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -6225,14 +5653,20 @@
       <xdr:row>86</xdr:row>
       <xdr:rowOff>124429</xdr:rowOff>
     </xdr:to>
-    <xdr:graphicFrame>
+    <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name="Диаграмма 2"/>
+        <xdr:cNvPr id="3" name="Диаграмма 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="0" y="16457930"/>
-        <a:ext cx="5328285" cy="2760345"/>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -6255,14 +5689,20 @@
       <xdr:row>86</xdr:row>
       <xdr:rowOff>113847</xdr:rowOff>
     </xdr:to>
-    <xdr:graphicFrame>
+    <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="5" name="Диаграмма 4"/>
+        <xdr:cNvPr id="5" name="Диаграмма 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000005000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="5954395" y="16447135"/>
-        <a:ext cx="5452110" cy="2760980"/>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -6285,14 +5725,20 @@
       <xdr:row>86</xdr:row>
       <xdr:rowOff>125186</xdr:rowOff>
     </xdr:to>
-    <xdr:graphicFrame>
+    <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="6" name="Диаграмма 5"/>
+        <xdr:cNvPr id="6" name="Диаграмма 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000006000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="11846560" y="16458565"/>
-        <a:ext cx="5681345" cy="2760980"/>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -6315,14 +5761,20 @@
       <xdr:row>103</xdr:row>
       <xdr:rowOff>44026</xdr:rowOff>
     </xdr:to>
-    <xdr:graphicFrame>
+    <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="8" name="Диаграмма 7"/>
+        <xdr:cNvPr id="8" name="Диаграмма 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000008000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="147320" y="19853275"/>
-        <a:ext cx="5334000" cy="2760980"/>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -6607,29 +6059,29 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M108"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="16.1"/>
+  <sheetFormatPr defaultColWidth="10.8125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="13.3286713286713" style="1" customWidth="1"/>
-    <col min="2" max="2" width="13.8321678321678" style="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5034965034965" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.3125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.8125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5" style="1" customWidth="1"/>
     <col min="4" max="4" width="13" style="1" customWidth="1"/>
-    <col min="5" max="6" width="12.1608391608392" style="1" customWidth="1"/>
-    <col min="7" max="7" width="11.3286713286713" style="1" customWidth="1"/>
-    <col min="8" max="8" width="12.3286713286713" style="1" customWidth="1"/>
+    <col min="5" max="6" width="12.1875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="11.3125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="12.3125" style="1" customWidth="1"/>
     <col min="9" max="9" width="11" style="1" customWidth="1"/>
-    <col min="10" max="10" width="12.3286713286713" style="1" customWidth="1"/>
+    <col min="10" max="10" width="12.3125" style="1" customWidth="1"/>
     <col min="11" max="13" width="13" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="10.8321678321678" style="1"/>
+    <col min="14" max="16384" width="10.8125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32.25" spans="1:13">
+    <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -6666,7 +6118,7 @@
       <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="9" t="s">
+      <c r="M1" s="7" t="s">
         <v>12</v>
       </c>
     </row>
@@ -6686,11 +6138,11 @@
       </c>
       <c r="E2" s="4">
         <f>B2-$B$25</f>
-        <v>-1.85</v>
+        <v>-1.8499999999999996</v>
       </c>
       <c r="F2" s="4">
         <f>E2^2</f>
-        <v>3.4225</v>
+        <v>3.4224999999999985</v>
       </c>
       <c r="G2" s="4">
         <f>C2-$C$25</f>
@@ -6702,23 +6154,23 @@
       </c>
       <c r="I2" s="4">
         <f>E2*G2</f>
-        <v>47.6375</v>
+        <v>47.637499999999989</v>
       </c>
       <c r="J2" s="4">
         <f t="shared" ref="J2:J21" si="0">$B$29+$A$29*B2</f>
-        <v>232.804531319414</v>
+        <v>232.80453131941363</v>
       </c>
       <c r="K2" s="4">
         <f>C2-J2</f>
-        <v>-10.8045313194136</v>
+        <v>-10.804531319413627</v>
       </c>
       <c r="L2" s="4">
         <f>K2^2</f>
-        <v>116.73789703219</v>
+        <v>116.73789703218998</v>
       </c>
       <c r="M2" s="4">
         <f>L2/($A$23-2)</f>
-        <v>6.48543872401055</v>
+        <v>6.485438724010554</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -6737,11 +6189,11 @@
       </c>
       <c r="E3" s="4">
         <f t="shared" ref="E3:E21" si="2">B3-$B$25</f>
-        <v>0.15</v>
+        <v>0.15000000000000036</v>
       </c>
       <c r="F3" s="4">
         <f t="shared" ref="F3:F21" si="3">E3^2</f>
-        <v>0.0225000000000001</v>
+        <v>2.2500000000000107E-2</v>
       </c>
       <c r="G3" s="4">
         <f t="shared" ref="G3:G21" si="4">C3-$C$25</f>
@@ -6753,11 +6205,11 @@
       </c>
       <c r="I3" s="4">
         <f t="shared" ref="I3:I21" si="6">E3*G3</f>
-        <v>-1.0125</v>
+        <v>-1.0125000000000024</v>
       </c>
       <c r="J3" s="4">
         <f t="shared" si="0"/>
-        <v>248.961794757885</v>
+        <v>248.9617947578854</v>
       </c>
       <c r="K3" s="4">
         <f t="shared" ref="K3:K21" si="7">C3-J3</f>
@@ -6765,11 +6217,11 @@
       </c>
       <c r="L3" s="4">
         <f t="shared" ref="L3:L21" si="8">K3^2</f>
-        <v>63.3901757666914</v>
+        <v>63.390175766691435</v>
       </c>
       <c r="M3" s="4">
         <f t="shared" ref="M3:M21" si="9">L3/($A$23-2)</f>
-        <v>3.52167643148286</v>
+        <v>3.5216764314828577</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -6788,11 +6240,11 @@
       </c>
       <c r="E4" s="4">
         <f t="shared" si="2"/>
-        <v>1.15</v>
+        <v>1.1500000000000004</v>
       </c>
       <c r="F4" s="4">
         <f t="shared" si="3"/>
-        <v>1.3225</v>
+        <v>1.3225000000000009</v>
       </c>
       <c r="G4" s="4">
         <f t="shared" si="4"/>
@@ -6804,23 +6256,23 @@
       </c>
       <c r="I4" s="4">
         <f t="shared" si="6"/>
-        <v>-5.4625</v>
+        <v>-5.4625000000000021</v>
       </c>
       <c r="J4" s="4">
         <f t="shared" si="0"/>
-        <v>257.040426477121</v>
+        <v>257.04042647712129</v>
       </c>
       <c r="K4" s="4">
         <f t="shared" si="7"/>
-        <v>-14.0404264771213</v>
+        <v>-14.040426477121287</v>
       </c>
       <c r="L4" s="4">
         <f t="shared" si="8"/>
-        <v>197.133575659448</v>
+        <v>197.13357565944847</v>
       </c>
       <c r="M4" s="4">
         <f t="shared" si="9"/>
-        <v>10.9518653144138</v>
+        <v>10.951865314413803</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -6839,11 +6291,11 @@
       </c>
       <c r="E5" s="4">
         <f t="shared" si="2"/>
-        <v>3.15</v>
+        <v>3.1500000000000004</v>
       </c>
       <c r="F5" s="4">
         <f t="shared" si="3"/>
-        <v>9.9225</v>
+        <v>9.922500000000003</v>
       </c>
       <c r="G5" s="4">
         <f t="shared" si="4"/>
@@ -6855,23 +6307,23 @@
       </c>
       <c r="I5" s="4">
         <f t="shared" si="6"/>
-        <v>117.3375</v>
+        <v>117.33750000000002</v>
       </c>
       <c r="J5" s="4">
         <f t="shared" si="0"/>
-        <v>273.197689915593</v>
+        <v>273.19768991559306</v>
       </c>
       <c r="K5" s="4">
         <f t="shared" si="7"/>
-        <v>11.8023100844069</v>
+        <v>11.80231008440694</v>
       </c>
       <c r="L5" s="4">
         <f t="shared" si="8"/>
-        <v>139.294523328494</v>
+        <v>139.29452332849377</v>
       </c>
       <c r="M5" s="4">
         <f t="shared" si="9"/>
-        <v>7.73858462936076</v>
+        <v>7.7385846293607647</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -6890,11 +6342,11 @@
       </c>
       <c r="E6" s="4">
         <f t="shared" si="2"/>
-        <v>2.15</v>
+        <v>2.1500000000000004</v>
       </c>
       <c r="F6" s="4">
         <f t="shared" si="3"/>
-        <v>4.6225</v>
+        <v>4.6225000000000014</v>
       </c>
       <c r="G6" s="4">
         <f t="shared" si="4"/>
@@ -6906,23 +6358,23 @@
       </c>
       <c r="I6" s="4">
         <f t="shared" si="6"/>
-        <v>11.2875</v>
+        <v>11.287500000000001</v>
       </c>
       <c r="J6" s="4">
         <f t="shared" si="0"/>
-        <v>265.119058196357</v>
+        <v>265.11905819635717</v>
       </c>
       <c r="K6" s="4">
         <f t="shared" si="7"/>
-        <v>-12.1190581963572</v>
+        <v>-12.119058196357173</v>
       </c>
       <c r="L6" s="4">
         <f t="shared" si="8"/>
-        <v>146.871571566692</v>
+        <v>146.87157156669198</v>
       </c>
       <c r="M6" s="4">
         <f t="shared" si="9"/>
-        <v>8.15953175370511</v>
+        <v>8.1595317537051102</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -6941,11 +6393,11 @@
       </c>
       <c r="E7" s="4">
         <f t="shared" si="2"/>
-        <v>-0.85</v>
+        <v>-0.84999999999999964</v>
       </c>
       <c r="F7" s="4">
         <f t="shared" si="3"/>
-        <v>0.722499999999999</v>
+        <v>0.72249999999999936</v>
       </c>
       <c r="G7" s="4">
         <f t="shared" si="4"/>
@@ -6957,23 +6409,23 @@
       </c>
       <c r="I7" s="4">
         <f t="shared" si="6"/>
-        <v>0.6375</v>
+        <v>0.63749999999999973</v>
       </c>
       <c r="J7" s="4">
         <f t="shared" si="0"/>
-        <v>240.88316303865</v>
+        <v>240.88316303864951</v>
       </c>
       <c r="K7" s="4">
         <f t="shared" si="7"/>
-        <v>6.11683696135049</v>
+        <v>6.1168369613504865</v>
       </c>
       <c r="L7" s="4">
         <f t="shared" si="8"/>
-        <v>37.4156944117435</v>
+        <v>37.415694411743452</v>
       </c>
       <c r="M7" s="4">
         <f t="shared" si="9"/>
-        <v>2.0786496895413</v>
+        <v>2.0786496895413027</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -6992,11 +6444,11 @@
       </c>
       <c r="E8" s="4">
         <f t="shared" si="2"/>
-        <v>-1.85</v>
+        <v>-1.8499999999999996</v>
       </c>
       <c r="F8" s="4">
         <f t="shared" si="3"/>
-        <v>3.4225</v>
+        <v>3.4224999999999985</v>
       </c>
       <c r="G8" s="4">
         <f t="shared" si="4"/>
@@ -7008,23 +6460,23 @@
       </c>
       <c r="I8" s="4">
         <f t="shared" si="6"/>
-        <v>3.2375</v>
+        <v>3.2374999999999994</v>
       </c>
       <c r="J8" s="4">
         <f t="shared" si="0"/>
-        <v>232.804531319414</v>
+        <v>232.80453131941363</v>
       </c>
       <c r="K8" s="4">
         <f t="shared" si="7"/>
-        <v>13.1954686805864</v>
+        <v>13.195468680586373</v>
       </c>
       <c r="L8" s="4">
         <f t="shared" si="8"/>
-        <v>174.120393700336</v>
+        <v>174.12039370033588</v>
       </c>
       <c r="M8" s="4">
         <f t="shared" si="9"/>
-        <v>9.67335520557422</v>
+        <v>9.6733552055742162</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -7043,11 +6495,11 @@
       </c>
       <c r="E9" s="4">
         <f t="shared" si="2"/>
-        <v>2.15</v>
+        <v>2.1500000000000004</v>
       </c>
       <c r="F9" s="4">
         <f t="shared" si="3"/>
-        <v>4.6225</v>
+        <v>4.6225000000000014</v>
       </c>
       <c r="G9" s="4">
         <f t="shared" si="4"/>
@@ -7059,23 +6511,23 @@
       </c>
       <c r="I9" s="4">
         <f t="shared" si="6"/>
-        <v>60.7375</v>
+        <v>60.737500000000011</v>
       </c>
       <c r="J9" s="4">
         <f t="shared" si="0"/>
-        <v>265.119058196357</v>
+        <v>265.11905819635717</v>
       </c>
       <c r="K9" s="4">
         <f t="shared" si="7"/>
-        <v>10.8809418036428</v>
+        <v>10.880941803642827</v>
       </c>
       <c r="L9" s="4">
         <f t="shared" si="8"/>
-        <v>118.394894534262</v>
+        <v>118.39489453426202</v>
       </c>
       <c r="M9" s="4">
         <f t="shared" si="9"/>
-        <v>6.57749414079233</v>
+        <v>6.5774941407923349</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -7094,11 +6546,11 @@
       </c>
       <c r="E10" s="4">
         <f t="shared" si="2"/>
-        <v>1.15</v>
+        <v>1.1500000000000004</v>
       </c>
       <c r="F10" s="4">
         <f t="shared" si="3"/>
-        <v>1.3225</v>
+        <v>1.3225000000000009</v>
       </c>
       <c r="G10" s="4">
         <f t="shared" si="4"/>
@@ -7110,23 +6562,23 @@
       </c>
       <c r="I10" s="4">
         <f t="shared" si="6"/>
-        <v>15.2375</v>
+        <v>15.237500000000004</v>
       </c>
       <c r="J10" s="4">
         <f t="shared" si="0"/>
-        <v>257.040426477121</v>
+        <v>257.04042647712129</v>
       </c>
       <c r="K10" s="4">
         <f t="shared" si="7"/>
-        <v>3.95957352287871</v>
+        <v>3.9595735228787134</v>
       </c>
       <c r="L10" s="4">
         <f t="shared" si="8"/>
-        <v>15.6782224830821</v>
+        <v>15.678222483082145</v>
       </c>
       <c r="M10" s="4">
         <f t="shared" si="9"/>
-        <v>0.87101236017123</v>
+        <v>0.87101236017123029</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -7145,11 +6597,11 @@
       </c>
       <c r="E11" s="4">
         <f t="shared" si="2"/>
-        <v>-0.85</v>
+        <v>-0.84999999999999964</v>
       </c>
       <c r="F11" s="4">
         <f t="shared" si="3"/>
-        <v>0.722499999999999</v>
+        <v>0.72249999999999936</v>
       </c>
       <c r="G11" s="4">
         <f t="shared" si="4"/>
@@ -7161,23 +6613,23 @@
       </c>
       <c r="I11" s="4">
         <f t="shared" si="6"/>
-        <v>-5.3125</v>
+        <v>-5.3124999999999982</v>
       </c>
       <c r="J11" s="4">
         <f t="shared" si="0"/>
-        <v>240.88316303865</v>
+        <v>240.88316303864951</v>
       </c>
       <c r="K11" s="4">
         <f t="shared" si="7"/>
-        <v>13.1168369613505</v>
+        <v>13.116836961350486</v>
       </c>
       <c r="L11" s="4">
         <f t="shared" si="8"/>
-        <v>172.05141187065</v>
+        <v>172.05141187065027</v>
       </c>
       <c r="M11" s="4">
         <f t="shared" si="9"/>
-        <v>9.55841177059168</v>
+        <v>9.5584117705916825</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -7196,11 +6648,11 @@
       </c>
       <c r="E12" s="4">
         <f t="shared" si="2"/>
-        <v>-2.85</v>
+        <v>-2.8499999999999996</v>
       </c>
       <c r="F12" s="4">
         <f t="shared" si="3"/>
-        <v>8.1225</v>
+        <v>8.1224999999999987</v>
       </c>
       <c r="G12" s="4">
         <f t="shared" si="4"/>
@@ -7212,23 +6664,23 @@
       </c>
       <c r="I12" s="4">
         <f t="shared" si="6"/>
-        <v>53.4375</v>
+        <v>53.437499999999993</v>
       </c>
       <c r="J12" s="4">
         <f t="shared" si="0"/>
-        <v>224.725899600178</v>
+        <v>224.72589960017771</v>
       </c>
       <c r="K12" s="4">
         <f t="shared" si="7"/>
-        <v>4.27410039982229</v>
+        <v>4.274100399822288</v>
       </c>
       <c r="L12" s="4">
         <f t="shared" si="8"/>
-        <v>18.267934227761</v>
+        <v>18.267934227761042</v>
       </c>
       <c r="M12" s="4">
         <f t="shared" si="9"/>
-        <v>1.01488523487561</v>
+        <v>1.0148852348756134</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -7247,11 +6699,11 @@
       </c>
       <c r="E13" s="4">
         <f t="shared" si="2"/>
-        <v>0.15</v>
+        <v>0.15000000000000036</v>
       </c>
       <c r="F13" s="4">
         <f t="shared" si="3"/>
-        <v>0.0225000000000001</v>
+        <v>2.2500000000000107E-2</v>
       </c>
       <c r="G13" s="4">
         <f t="shared" si="4"/>
@@ -7263,23 +6715,23 @@
       </c>
       <c r="I13" s="4">
         <f t="shared" si="6"/>
-        <v>0.1875</v>
+        <v>0.18750000000000044</v>
       </c>
       <c r="J13" s="4">
         <f t="shared" si="0"/>
-        <v>248.961794757885</v>
+        <v>248.9617947578854</v>
       </c>
       <c r="K13" s="4">
         <f t="shared" si="7"/>
-        <v>0.0382052421146</v>
+        <v>3.8205242114599969E-2</v>
       </c>
       <c r="L13" s="4">
         <f t="shared" si="8"/>
-        <v>0.0014596405250352</v>
+        <v>1.4596405250352031E-3</v>
       </c>
       <c r="M13" s="4">
         <f t="shared" si="9"/>
-        <v>8.10911402797335e-5</v>
+        <v>8.1091140279733508E-5</v>
       </c>
     </row>
     <row r="14" spans="1:13">
@@ -7298,11 +6750,11 @@
       </c>
       <c r="E14" s="4">
         <f t="shared" si="2"/>
-        <v>1.15</v>
+        <v>1.1500000000000004</v>
       </c>
       <c r="F14" s="4">
         <f t="shared" si="3"/>
-        <v>1.3225</v>
+        <v>1.3225000000000009</v>
       </c>
       <c r="G14" s="4">
         <f t="shared" si="4"/>
@@ -7314,23 +6766,23 @@
       </c>
       <c r="I14" s="4">
         <f t="shared" si="6"/>
-        <v>4.8875</v>
+        <v>4.8875000000000011</v>
       </c>
       <c r="J14" s="4">
         <f t="shared" si="0"/>
-        <v>257.040426477121</v>
+        <v>257.04042647712129</v>
       </c>
       <c r="K14" s="4">
         <f t="shared" si="7"/>
-        <v>-5.04042647712129</v>
+        <v>-5.0404264771212866</v>
       </c>
       <c r="L14" s="4">
         <f t="shared" si="8"/>
-        <v>25.4058990712653</v>
+        <v>25.405899071265303</v>
       </c>
       <c r="M14" s="4">
         <f t="shared" si="9"/>
-        <v>1.41143883729252</v>
+        <v>1.4114388372925168</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -7349,11 +6801,11 @@
       </c>
       <c r="E15" s="4">
         <f t="shared" si="2"/>
-        <v>3.15</v>
+        <v>3.1500000000000004</v>
       </c>
       <c r="F15" s="4">
         <f t="shared" si="3"/>
-        <v>9.9225</v>
+        <v>9.922500000000003</v>
       </c>
       <c r="G15" s="4">
         <f t="shared" si="4"/>
@@ -7365,23 +6817,23 @@
       </c>
       <c r="I15" s="4">
         <f t="shared" si="6"/>
-        <v>98.4375</v>
+        <v>98.437500000000014</v>
       </c>
       <c r="J15" s="4">
         <f t="shared" si="0"/>
-        <v>273.197689915593</v>
+        <v>273.19768991559306</v>
       </c>
       <c r="K15" s="4">
         <f t="shared" si="7"/>
-        <v>5.80231008440694</v>
+        <v>5.8023100844069404</v>
       </c>
       <c r="L15" s="4">
         <f t="shared" si="8"/>
-        <v>33.6668023156105</v>
+        <v>33.666802315610475</v>
       </c>
       <c r="M15" s="4">
         <f t="shared" si="9"/>
-        <v>1.8703779064228</v>
+        <v>1.8703779064228041</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -7400,11 +6852,11 @@
       </c>
       <c r="E16" s="4">
         <f t="shared" si="2"/>
-        <v>2.15</v>
+        <v>2.1500000000000004</v>
       </c>
       <c r="F16" s="4">
         <f t="shared" si="3"/>
-        <v>4.6225</v>
+        <v>4.6225000000000014</v>
       </c>
       <c r="G16" s="4">
         <f t="shared" si="4"/>
@@ -7416,23 +6868,23 @@
       </c>
       <c r="I16" s="4">
         <f t="shared" si="6"/>
-        <v>30.6375</v>
+        <v>30.637500000000006</v>
       </c>
       <c r="J16" s="4">
         <f t="shared" si="0"/>
-        <v>265.119058196357</v>
+        <v>265.11905819635717</v>
       </c>
       <c r="K16" s="4">
         <f t="shared" si="7"/>
-        <v>-3.11905819635717</v>
+        <v>-3.1190581963571731</v>
       </c>
       <c r="L16" s="4">
         <f t="shared" si="8"/>
-        <v>9.72852403226286</v>
+        <v>9.728524032262861</v>
       </c>
       <c r="M16" s="4">
         <f t="shared" si="9"/>
-        <v>0.540473557347937</v>
+        <v>0.54047355734793667</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -7451,11 +6903,11 @@
       </c>
       <c r="E17" s="4">
         <f t="shared" si="2"/>
-        <v>4.15</v>
+        <v>4.1500000000000004</v>
       </c>
       <c r="F17" s="4">
         <f t="shared" si="3"/>
-        <v>17.2225</v>
+        <v>17.222500000000004</v>
       </c>
       <c r="G17" s="4">
         <f t="shared" si="4"/>
@@ -7467,23 +6919,23 @@
       </c>
       <c r="I17" s="4">
         <f t="shared" si="6"/>
-        <v>113.0875</v>
+        <v>113.08750000000001</v>
       </c>
       <c r="J17" s="4">
         <f t="shared" si="0"/>
-        <v>281.276321634829</v>
+        <v>281.27632163482895</v>
       </c>
       <c r="K17" s="4">
         <f t="shared" si="7"/>
-        <v>-6.27632163482895</v>
+        <v>-6.2763216348289461</v>
       </c>
       <c r="L17" s="4">
         <f t="shared" si="8"/>
-        <v>39.3922132638219</v>
+        <v>39.392213263821894</v>
       </c>
       <c r="M17" s="4">
         <f t="shared" si="9"/>
-        <v>2.18845629243455</v>
+        <v>2.1884562924345499</v>
       </c>
     </row>
     <row r="18" spans="1:13">
@@ -7502,11 +6954,11 @@
       </c>
       <c r="E18" s="4">
         <f t="shared" si="2"/>
-        <v>-3.85</v>
+        <v>-3.8499999999999996</v>
       </c>
       <c r="F18" s="4">
         <f t="shared" si="3"/>
-        <v>14.8225</v>
+        <v>14.822499999999998</v>
       </c>
       <c r="G18" s="4">
         <f t="shared" si="4"/>
@@ -7518,23 +6970,23 @@
       </c>
       <c r="I18" s="4">
         <f t="shared" si="6"/>
-        <v>141.4875</v>
+        <v>141.48749999999998</v>
       </c>
       <c r="J18" s="4">
         <f t="shared" si="0"/>
-        <v>216.647267880942</v>
+        <v>216.64726788094183</v>
       </c>
       <c r="K18" s="4">
         <f t="shared" si="7"/>
-        <v>-5.64726788094183</v>
+        <v>-5.6472678809418255</v>
       </c>
       <c r="L18" s="4">
         <f t="shared" si="8"/>
-        <v>31.8916345191172</v>
+        <v>31.891634519117176</v>
       </c>
       <c r="M18" s="4">
         <f t="shared" si="9"/>
-        <v>1.77175747328429</v>
+        <v>1.7717574732842876</v>
       </c>
     </row>
     <row r="19" spans="1:13">
@@ -7553,11 +7005,11 @@
       </c>
       <c r="E19" s="4">
         <f t="shared" si="2"/>
-        <v>-2.85</v>
+        <v>-2.8499999999999996</v>
       </c>
       <c r="F19" s="4">
         <f t="shared" si="3"/>
-        <v>8.1225</v>
+        <v>8.1224999999999987</v>
       </c>
       <c r="G19" s="4">
         <f t="shared" si="4"/>
@@ -7569,23 +7021,23 @@
       </c>
       <c r="I19" s="4">
         <f t="shared" si="6"/>
-        <v>79.0875</v>
+        <v>79.087499999999991</v>
       </c>
       <c r="J19" s="4">
         <f t="shared" si="0"/>
-        <v>224.725899600178</v>
+        <v>224.72589960017771</v>
       </c>
       <c r="K19" s="4">
         <f t="shared" si="7"/>
-        <v>-4.72589960017771</v>
+        <v>-4.725899600177712</v>
       </c>
       <c r="L19" s="4">
         <f t="shared" si="8"/>
-        <v>22.3341270309599</v>
+        <v>22.334127030959859</v>
       </c>
       <c r="M19" s="4">
         <f t="shared" si="9"/>
-        <v>1.24078483505333</v>
+        <v>1.2407848350533255</v>
       </c>
     </row>
     <row r="20" spans="1:13">
@@ -7604,11 +7056,11 @@
       </c>
       <c r="E20" s="4">
         <f t="shared" si="2"/>
-        <v>-3.85</v>
+        <v>-3.8499999999999996</v>
       </c>
       <c r="F20" s="4">
         <f t="shared" si="3"/>
-        <v>14.8225</v>
+        <v>14.822499999999998</v>
       </c>
       <c r="G20" s="4">
         <f t="shared" si="4"/>
@@ -7620,23 +7072,23 @@
       </c>
       <c r="I20" s="4">
         <f t="shared" si="6"/>
-        <v>114.5375</v>
+        <v>114.53749999999999</v>
       </c>
       <c r="J20" s="4">
         <f t="shared" si="0"/>
-        <v>216.647267880942</v>
+        <v>216.64726788094183</v>
       </c>
       <c r="K20" s="4">
         <f t="shared" si="7"/>
-        <v>1.35273211905817</v>
+        <v>1.3527321190581745</v>
       </c>
       <c r="L20" s="4">
         <f t="shared" si="8"/>
-        <v>1.82988418593162</v>
+        <v>1.8298841859316191</v>
       </c>
       <c r="M20" s="4">
         <f t="shared" si="9"/>
-        <v>0.101660232551757</v>
+        <v>0.10166023255175662</v>
       </c>
     </row>
     <row r="21" spans="1:13">
@@ -7655,11 +7107,11 @@
       </c>
       <c r="E21" s="4">
         <f t="shared" si="2"/>
-        <v>-1.85</v>
+        <v>-1.8499999999999996</v>
       </c>
       <c r="F21" s="4">
         <f t="shared" si="3"/>
-        <v>3.4225</v>
+        <v>3.4224999999999985</v>
       </c>
       <c r="G21" s="4">
         <f t="shared" si="4"/>
@@ -7671,26 +7123,26 @@
       </c>
       <c r="I21" s="4">
         <f t="shared" si="6"/>
-        <v>29.1375</v>
+        <v>29.137499999999996</v>
       </c>
       <c r="J21" s="4">
         <f t="shared" si="0"/>
-        <v>232.804531319414</v>
+        <v>232.80453131941363</v>
       </c>
       <c r="K21" s="4">
         <f t="shared" si="7"/>
-        <v>-0.804531319413627</v>
+        <v>-0.80453131941362699</v>
       </c>
       <c r="L21" s="4">
         <f t="shared" si="8"/>
-        <v>0.647270643917431</v>
+        <v>0.6472706439174315</v>
       </c>
       <c r="M21" s="4">
         <f t="shared" si="9"/>
-        <v>0.0359594802176351</v>
+        <v>3.5959480217635086E-2</v>
       </c>
     </row>
-    <row r="22" ht="16.15" spans="1:13">
+    <row r="22" spans="1:13">
       <c r="A22" s="2" t="s">
         <v>13</v>
       </c>
@@ -7770,7 +7222,7 @@
       </c>
       <c r="J23" s="2">
         <f t="shared" ref="J23:M23" si="11">SUM(J2:J21)</f>
-        <v>4955</v>
+        <v>4954.9999999999991</v>
       </c>
       <c r="K23" s="4">
         <f>ROUND(SUM(K2:K21),10)</f>
@@ -7778,14 +7230,14 @@
       </c>
       <c r="L23" s="2">
         <f t="shared" si="11"/>
-        <v>1364.25410928476</v>
+        <v>1364.2541092847623</v>
       </c>
       <c r="M23" s="2">
         <f t="shared" si="11"/>
-        <v>75.7918949602645</v>
+        <v>75.791894960264543</v>
       </c>
     </row>
-    <row r="24" ht="16.15" spans="2:13">
+    <row r="24" spans="1:13">
       <c r="B24" s="2" t="s">
         <v>15</v>
       </c>
@@ -7823,7 +7275,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="25" spans="2:13">
+    <row r="25" spans="1:13">
       <c r="B25" s="2">
         <f>AVERAGE(B2:B21)</f>
         <v>15.85</v>
@@ -7834,7 +7286,7 @@
       </c>
       <c r="D25" s="2">
         <f t="shared" ref="D25:I25" si="12">AVERAGE(D2:D21)</f>
-        <v>256.85</v>
+        <v>256.85000000000002</v>
       </c>
       <c r="E25" s="4">
         <f>ROUND(AVERAGE(E2:E21),10)</f>
@@ -7842,7 +7294,7 @@
       </c>
       <c r="F25" s="2">
         <f t="shared" si="12"/>
-        <v>5.6275</v>
+        <v>5.6274999999999995</v>
       </c>
       <c r="G25" s="4">
         <f t="shared" si="12"/>
@@ -7850,15 +7302,15 @@
       </c>
       <c r="H25" s="2">
         <f t="shared" si="12"/>
-        <v>435.4875</v>
+        <v>435.48750000000001</v>
       </c>
       <c r="I25" s="2">
         <f t="shared" si="12"/>
-        <v>45.4625</v>
+        <v>45.462499999999999</v>
       </c>
       <c r="J25" s="2">
         <f t="shared" ref="J25:M25" si="13">AVERAGE(J2:J21)</f>
-        <v>247.75</v>
+        <v>247.74999999999994</v>
       </c>
       <c r="K25" s="4">
         <f>ROUND(AVERAGE(K2:K21),10)</f>
@@ -7866,14 +7318,14 @@
       </c>
       <c r="L25" s="2">
         <f t="shared" si="13"/>
-        <v>68.2127054642381</v>
+        <v>68.212705464238113</v>
       </c>
       <c r="M25" s="2">
         <f t="shared" si="13"/>
-        <v>3.78959474801323</v>
+        <v>3.789594748013227</v>
       </c>
     </row>
-    <row r="28" ht="16.15" spans="1:6">
+    <row r="28" spans="1:13">
       <c r="A28" s="2" t="s">
         <v>16</v>
       </c>
@@ -7893,38 +7345,38 @@
         <v>21</v>
       </c>
     </row>
-    <row r="29" spans="1:6">
+    <row r="29" spans="1:13">
       <c r="A29" s="4">
         <f>I23/F23</f>
-        <v>8.0786317192359</v>
+        <v>8.0786317192358954</v>
       </c>
       <c r="B29" s="4">
         <f>C25-A29*B25</f>
-        <v>119.703687250111</v>
+        <v>119.70368725011107</v>
       </c>
       <c r="C29" s="4">
         <f>M23/(A23*(D25-B25^2))</f>
-        <v>0.673406441228469</v>
+        <v>0.67340644122846904</v>
       </c>
       <c r="D29" s="4">
         <f>C29*D25</f>
-        <v>172.964444429532</v>
+        <v>172.96444442953228</v>
       </c>
       <c r="E29" s="4">
         <f>A29/SQRT(C29)</f>
-        <v>9.84462499097719</v>
+        <v>9.8446249909771932</v>
       </c>
       <c r="F29" s="4">
         <f>B29/SQRT(D29)</f>
-        <v>9.10183818304628</v>
+        <v>9.1018381830462811</v>
       </c>
     </row>
-    <row r="32" ht="18" customHeight="1" spans="1:3">
+    <row r="32" spans="1:13" ht="18" customHeight="1">
       <c r="A32" s="5"/>
       <c r="B32" s="5"/>
       <c r="C32" s="5"/>
     </row>
-    <row r="33" ht="48.4" spans="1:4">
+    <row r="33" spans="1:5" ht="45">
       <c r="A33" s="2" t="s">
         <v>22</v>
       </c>
@@ -7938,13 +7390,13 @@
         <v>25</v>
       </c>
     </row>
-    <row r="34" ht="16.15" spans="1:4">
+    <row r="34" spans="1:5">
       <c r="A34" s="2">
         <v>0.9</v>
       </c>
       <c r="B34" s="4">
         <f>TINV(1-A34,$A$23-2)</f>
-        <v>1.73406360661754</v>
+        <v>1.7340636066175394</v>
       </c>
       <c r="C34" s="2" t="str">
         <f>IF(E$29&gt;$B34,"значимый","не значимый")</f>
@@ -7955,13 +7407,13 @@
         <v>значимый</v>
       </c>
     </row>
-    <row r="35" ht="16.15" spans="1:4">
+    <row r="35" spans="1:5">
       <c r="A35" s="2">
         <v>0.95</v>
       </c>
       <c r="B35" s="4">
         <f>TINV(1-A35,$A$23-2)</f>
-        <v>2.10092204024104</v>
+        <v>2.1009220402410378</v>
       </c>
       <c r="C35" s="2" t="str">
         <f t="shared" ref="C35:C36" si="14">IF(E$29&gt;$B35,"значимый","не значимый")</f>
@@ -7972,13 +7424,13 @@
         <v>значимый</v>
       </c>
     </row>
-    <row r="36" ht="16.15" spans="1:4">
+    <row r="36" spans="1:5">
       <c r="A36" s="2">
         <v>0.99</v>
       </c>
       <c r="B36" s="4">
         <f>TINV(1-A36,$A$23-2)</f>
-        <v>2.87844047273861</v>
+        <v>2.8784404727386073</v>
       </c>
       <c r="C36" s="2" t="str">
         <f t="shared" si="14"/>
@@ -7989,7 +7441,7 @@
         <v>значимый</v>
       </c>
     </row>
-    <row r="39" ht="16.15" spans="1:4">
+    <row r="39" spans="1:5">
       <c r="A39" s="2" t="s">
         <v>22</v>
       </c>
@@ -8003,8 +7455,8 @@
         <v>17</v>
       </c>
     </row>
-    <row r="40" ht="16.15" spans="1:4">
-      <c r="A40" s="2">
+    <row r="40" spans="1:5">
+      <c r="A40" s="8">
         <v>0.9</v>
       </c>
       <c r="B40" s="2" t="s">
@@ -8012,29 +7464,29 @@
       </c>
       <c r="C40" s="4">
         <f>A$29-$B34*SQRT(C$29)</f>
-        <v>6.65563579319174</v>
+        <v>6.6556357931917374</v>
       </c>
       <c r="D40" s="4">
         <f>B$29-$B34*SQRT(D$29)</f>
-        <v>96.8979854277048</v>
+        <v>96.897985427704796</v>
       </c>
     </row>
-    <row r="41" ht="16.15" spans="1:4">
-      <c r="A41" s="2"/>
+    <row r="41" spans="1:5">
+      <c r="A41" s="8"/>
       <c r="B41" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C41" s="4">
         <f>A$29+$B34*SQRT(C$29)</f>
-        <v>9.50162764528005</v>
+        <v>9.5016276452800525</v>
       </c>
       <c r="D41" s="4">
         <f>B$29+$B34*SQRT(D$29)</f>
-        <v>142.509389072517</v>
+        <v>142.50938907251734</v>
       </c>
     </row>
-    <row r="42" ht="16.15" spans="1:4">
-      <c r="A42" s="2">
+    <row r="42" spans="1:5">
+      <c r="A42" s="8">
         <v>0.95</v>
       </c>
       <c r="B42" s="2" t="s">
@@ -8042,29 +7494,29 @@
       </c>
       <c r="C42" s="4">
         <f>A$29-$B35*SQRT(C$29)</f>
-        <v>6.35458682677034</v>
+        <v>6.3545868267703352</v>
       </c>
       <c r="D42" s="4">
         <f>B$29-$B35*SQRT(D$29)</f>
-        <v>92.0732119786085</v>
+        <v>92.07321197860847</v>
       </c>
     </row>
-    <row r="43" ht="16.15" spans="1:4">
-      <c r="A43" s="2"/>
+    <row r="43" spans="1:5">
+      <c r="A43" s="8"/>
       <c r="B43" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C43" s="4">
         <f>A$29+$B35*SQRT(C$29)</f>
-        <v>9.80267661170146</v>
+        <v>9.8026766117014557</v>
       </c>
       <c r="D43" s="4">
         <f>B$29+$B35*SQRT(D$29)</f>
-        <v>147.334162521614</v>
+        <v>147.33416252161368</v>
       </c>
     </row>
-    <row r="44" ht="16.15" spans="1:4">
-      <c r="A44" s="2">
+    <row r="44" spans="1:5">
+      <c r="A44" s="8">
         <v>0.99</v>
       </c>
       <c r="B44" s="2" t="s">
@@ -8072,44 +7524,44 @@
       </c>
       <c r="C44" s="4">
         <f>A$29-$B36*SQRT(C$29)</f>
-        <v>5.71654474016751</v>
+        <v>5.7165447401675067</v>
       </c>
       <c r="D44" s="4">
         <f>B$29-$B36*SQRT(D$29)</f>
-        <v>81.847604644889</v>
+        <v>81.847604644889032</v>
       </c>
     </row>
-    <row r="45" ht="16.15" spans="1:4">
-      <c r="A45" s="2"/>
+    <row r="45" spans="1:5">
+      <c r="A45" s="8"/>
       <c r="B45" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C45" s="4">
         <f>A$29+$B36*SQRT(C$29)</f>
-        <v>10.4407186983043</v>
+        <v>10.440718698304284</v>
       </c>
       <c r="D45" s="4">
         <f>B$29+$B36*SQRT(D$29)</f>
-        <v>157.559769855333</v>
+        <v>157.55976985533312</v>
       </c>
     </row>
-    <row r="47" ht="51" customHeight="1" spans="1:5">
+    <row r="47" spans="1:5" ht="51" customHeight="1">
       <c r="A47" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C47" s="2" t="s">
+      <c r="C47" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="D47" s="2"/>
-      <c r="E47" s="2"/>
+      <c r="D47" s="8"/>
+      <c r="E47" s="8"/>
     </row>
-    <row r="48" spans="1:1">
+    <row r="48" spans="1:5">
       <c r="A48" s="2">
         <f>1-L23/H23</f>
-        <v>0.8433647223761</v>
+        <v>0.84336472237610005</v>
       </c>
     </row>
-    <row r="50" ht="48.4" spans="1:3">
+    <row r="50" spans="1:8" ht="45">
       <c r="A50" s="2" t="s">
         <v>22</v>
       </c>
@@ -8120,101 +7572,101 @@
         <v>32</v>
       </c>
     </row>
-    <row r="51" ht="17" customHeight="1" spans="1:3">
-      <c r="A51" s="2">
+    <row r="51" spans="1:8" ht="17.05" customHeight="1">
+      <c r="A51" s="8">
         <v>0.9</v>
       </c>
-      <c r="B51" s="6">
+      <c r="B51" s="9">
         <f>FINV(1-A51,2,$A$23-2)</f>
-        <v>2.62394698513396</v>
-      </c>
-      <c r="C51" s="2" t="str">
+        <v>2.6239469851339554</v>
+      </c>
+      <c r="C51" s="8" t="str">
         <f>IF($B$58&gt;B51,"значимый","не значимый")</f>
         <v>значимый</v>
       </c>
     </row>
-    <row r="52" spans="1:3">
-      <c r="A52" s="2"/>
-      <c r="B52" s="7"/>
-      <c r="C52" s="2"/>
+    <row r="52" spans="1:8">
+      <c r="A52" s="8"/>
+      <c r="B52" s="10"/>
+      <c r="C52" s="8"/>
     </row>
-    <row r="53" ht="16" customHeight="1" spans="1:3">
-      <c r="A53" s="2">
+    <row r="53" spans="1:8" ht="16" customHeight="1">
+      <c r="A53" s="8">
         <v>0.95</v>
       </c>
-      <c r="B53" s="6">
+      <c r="B53" s="9">
         <f t="shared" ref="B53" si="16">FINV(1-A53,2,$A$23-2)</f>
-        <v>3.55455714566179</v>
-      </c>
-      <c r="C53" s="2" t="str">
+        <v>3.5545571456617857</v>
+      </c>
+      <c r="C53" s="8" t="str">
         <f t="shared" ref="C53" si="17">IF($B$58&gt;B53,"значимый","не значимый")</f>
         <v>значимый</v>
       </c>
     </row>
-    <row r="54" spans="1:3">
-      <c r="A54" s="2"/>
-      <c r="B54" s="7"/>
-      <c r="C54" s="2"/>
+    <row r="54" spans="1:8">
+      <c r="A54" s="8"/>
+      <c r="B54" s="10"/>
+      <c r="C54" s="8"/>
     </row>
-    <row r="55" ht="16" customHeight="1" spans="1:3">
-      <c r="A55" s="2">
+    <row r="55" spans="1:8" ht="16" customHeight="1">
+      <c r="A55" s="8">
         <v>0.99</v>
       </c>
-      <c r="B55" s="6">
+      <c r="B55" s="9">
         <f t="shared" ref="B55" si="18">FINV(1-A55,2,$A$23-2)</f>
-        <v>6.01290483480053</v>
-      </c>
-      <c r="C55" s="2" t="str">
+        <v>6.0129048348005281</v>
+      </c>
+      <c r="C55" s="8" t="str">
         <f t="shared" ref="C55" si="19">IF($B$58&gt;B55,"значимый","не значимый")</f>
         <v>значимый</v>
       </c>
     </row>
-    <row r="56" spans="1:3">
-      <c r="A56" s="2"/>
-      <c r="B56" s="7"/>
-      <c r="C56" s="2"/>
+    <row r="56" spans="1:8">
+      <c r="A56" s="8"/>
+      <c r="B56" s="10"/>
+      <c r="C56" s="8"/>
     </row>
-    <row r="57" spans="2:2">
-      <c r="B57" s="8"/>
+    <row r="57" spans="1:8">
+      <c r="B57" s="6"/>
     </row>
-    <row r="58" ht="16.15" spans="1:2">
+    <row r="58" spans="1:8">
       <c r="A58" s="2" t="s">
         <v>33</v>
       </c>
       <c r="B58" s="4">
         <f>A48/(1-A48)*(A23-2)</f>
-        <v>96.9166412129722</v>
+        <v>96.916641212972181</v>
       </c>
     </row>
-    <row r="61" ht="16" customHeight="1" spans="3:8">
-      <c r="C61" s="2" t="s">
+    <row r="61" spans="1:8" ht="16" customHeight="1">
+      <c r="C61" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="D61" s="2"/>
-      <c r="E61" s="2"/>
-      <c r="F61" s="2"/>
-      <c r="G61" s="2"/>
-      <c r="H61" s="2"/>
+      <c r="D61" s="8"/>
+      <c r="E61" s="8"/>
+      <c r="F61" s="8"/>
+      <c r="G61" s="8"/>
+      <c r="H61" s="8"/>
     </row>
-    <row r="62" ht="16.15" spans="1:8">
+    <row r="62" spans="1:8">
       <c r="A62" s="2" t="s">
         <v>34</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C62" s="2">
+      <c r="C62" s="8">
         <v>0.9</v>
       </c>
-      <c r="D62" s="2"/>
-      <c r="E62" s="2">
+      <c r="D62" s="8"/>
+      <c r="E62" s="8">
         <v>0.95</v>
       </c>
-      <c r="F62" s="2"/>
-      <c r="G62" s="2">
+      <c r="F62" s="8"/>
+      <c r="G62" s="8">
         <v>0.99</v>
       </c>
-      <c r="H62" s="2"/>
+      <c r="H62" s="8"/>
     </row>
     <row r="63" spans="1:8">
       <c r="A63" s="2">
@@ -8222,31 +7674,31 @@
       </c>
       <c r="B63" s="4">
         <f>$B$29+A63*$A$29</f>
-        <v>216.647267880942</v>
+        <v>216.64726788094183</v>
       </c>
       <c r="C63" s="4">
         <f>B63-$B$34*SQRT($M$23)*SQRT(1/$A$23+(A63-$B$25)^2/($F$23))</f>
-        <v>210.212241778178</v>
+        <v>210.21224177817754</v>
       </c>
       <c r="D63" s="4">
         <f>B63+$B$34*SQRT($M$23)*SQRT(1/$A$23+(A63-$B$25)^2/($F$23))</f>
-        <v>223.082293983706</v>
+        <v>223.08229398370611</v>
       </c>
       <c r="E63" s="4">
         <f>B63-$B$35*SQRT($M$23)*SQRT(1/$A$23+(A63-$B$25)^2/($F$23))</f>
-        <v>208.850847889639</v>
+        <v>208.85084788963886</v>
       </c>
       <c r="F63" s="4">
         <f>B63+$B$35*SQRT($M$23)*SQRT(1/$A$23+(A63-$B$25)^2/($F$23))</f>
-        <v>224.443687872245</v>
+        <v>224.44368787224479</v>
       </c>
       <c r="G63" s="4">
         <f>B63-$B$36*SQRT($M$23)*SQRT(1/$A$23+(A63-$B$25)^2/($F$23))</f>
-        <v>205.965514624234</v>
+        <v>205.96551462423358</v>
       </c>
       <c r="H63" s="4">
         <f>B63+$B$36*SQRT($M$23)*SQRT(1/$A$23+(A63-$B$25)^2/($F$23))</f>
-        <v>227.32902113765</v>
+        <v>227.32902113765007</v>
       </c>
     </row>
     <row r="64" spans="1:8">
@@ -8255,31 +7707,31 @@
       </c>
       <c r="B64" s="4">
         <f t="shared" ref="B64:B71" si="20">$B$29+A64*$A$29</f>
-        <v>224.725899600178</v>
+        <v>224.72589960017771</v>
       </c>
       <c r="C64" s="4">
         <f t="shared" ref="C64:C71" si="21">B64-$B$34*SQRT($M$23)*SQRT(1/$A$23+(A64-$B$25)^2/($F$23))</f>
-        <v>219.449289483242</v>
+        <v>219.4492894832417</v>
       </c>
       <c r="D64" s="4">
         <f t="shared" ref="D64:D71" si="22">B64+$B$34*SQRT($M$23)*SQRT(1/$A$23+(A64-$B$25)^2/($F$23))</f>
-        <v>230.002509717114</v>
+        <v>230.00250971711372</v>
       </c>
       <c r="E64" s="4">
         <f t="shared" ref="E64:E71" si="23">B64-$B$35*SQRT($M$23)*SQRT(1/$A$23+(A64-$B$25)^2/($F$23))</f>
-        <v>218.332970038584</v>
+        <v>218.33297003858365</v>
       </c>
       <c r="F64" s="4">
         <f t="shared" ref="F64:F71" si="24">B64+$B$35*SQRT($M$23)*SQRT(1/$A$23+(A64-$B$25)^2/($F$23))</f>
-        <v>231.118829161772</v>
+        <v>231.11882916177177</v>
       </c>
       <c r="G64" s="4">
         <f t="shared" ref="G64:G71" si="25">B64-$B$36*SQRT($M$23)*SQRT(1/$A$23+(A64-$B$25)^2/($F$23))</f>
-        <v>215.9670466599</v>
+        <v>215.96704665990001</v>
       </c>
       <c r="H64" s="4">
         <f t="shared" ref="H64:H71" si="26">B64+$B$36*SQRT($M$23)*SQRT(1/$A$23+(A64-$B$25)^2/($F$23))</f>
-        <v>233.484752540455</v>
+        <v>233.48475254045542</v>
       </c>
     </row>
     <row r="65" spans="1:8">
@@ -8288,31 +7740,31 @@
       </c>
       <c r="B65" s="4">
         <f t="shared" si="20"/>
-        <v>232.804531319414</v>
+        <v>232.80453131941363</v>
       </c>
       <c r="C65" s="4">
         <f t="shared" si="21"/>
-        <v>228.523701666166</v>
+        <v>228.52370166616632</v>
       </c>
       <c r="D65" s="4">
         <f t="shared" si="22"/>
-        <v>237.085360972661</v>
+        <v>237.08536097266094</v>
       </c>
       <c r="E65" s="4">
         <f t="shared" si="23"/>
-        <v>227.618049500233</v>
+        <v>227.61804950023298</v>
       </c>
       <c r="F65" s="4">
         <f t="shared" si="24"/>
-        <v>237.991013138594</v>
+        <v>237.99101313859427</v>
       </c>
       <c r="G65" s="4">
         <f t="shared" si="25"/>
-        <v>225.69861358734</v>
+        <v>225.69861358734028</v>
       </c>
       <c r="H65" s="4">
         <f t="shared" si="26"/>
-        <v>239.910449051487</v>
+        <v>239.91044905148698</v>
       </c>
     </row>
     <row r="66" spans="1:8">
@@ -8321,31 +7773,31 @@
       </c>
       <c r="B66" s="4">
         <f t="shared" si="20"/>
-        <v>240.88316303865</v>
+        <v>240.88316303864951</v>
       </c>
       <c r="C66" s="4">
         <f t="shared" si="21"/>
-        <v>237.297326242981</v>
+        <v>237.29732624298131</v>
       </c>
       <c r="D66" s="4">
         <f t="shared" si="22"/>
-        <v>244.468999834318</v>
+        <v>244.46899983431771</v>
       </c>
       <c r="E66" s="4">
         <f t="shared" si="23"/>
-        <v>236.538706740751</v>
+        <v>236.53870674075074</v>
       </c>
       <c r="F66" s="4">
         <f t="shared" si="24"/>
-        <v>245.227619336548</v>
+        <v>245.22761933654829</v>
       </c>
       <c r="G66" s="4">
         <f t="shared" si="25"/>
-        <v>234.93089132157</v>
+        <v>234.93089132156987</v>
       </c>
       <c r="H66" s="4">
         <f t="shared" si="26"/>
-        <v>246.835434755729</v>
+        <v>246.83543475572915</v>
       </c>
     </row>
     <row r="67" spans="1:8">
@@ -8354,31 +7806,31 @@
       </c>
       <c r="B67" s="4">
         <f t="shared" si="20"/>
-        <v>248.961794757885</v>
+        <v>248.9617947578854</v>
       </c>
       <c r="C67" s="4">
         <f t="shared" si="21"/>
-        <v>245.579372054956</v>
+        <v>245.57937205495614</v>
       </c>
       <c r="D67" s="4">
         <f t="shared" si="22"/>
-        <v>252.344217460815</v>
+        <v>252.34421746081466</v>
       </c>
       <c r="E67" s="4">
         <f t="shared" si="23"/>
-        <v>244.863786830796</v>
+        <v>244.8637868307961</v>
       </c>
       <c r="F67" s="4">
         <f t="shared" si="24"/>
-        <v>253.059802684975</v>
+        <v>253.0598026849747</v>
       </c>
       <c r="G67" s="4">
         <f t="shared" si="25"/>
-        <v>243.34717810434</v>
+        <v>243.3471781043402</v>
       </c>
       <c r="H67" s="4">
         <f t="shared" si="26"/>
-        <v>254.576411411431</v>
+        <v>254.5764114114306</v>
       </c>
     </row>
     <row r="68" spans="1:8">
@@ -8387,31 +7839,31 @@
       </c>
       <c r="B68" s="4">
         <f t="shared" si="20"/>
-        <v>257.040426477121</v>
+        <v>257.04042647712129</v>
       </c>
       <c r="C68" s="4">
         <f t="shared" si="21"/>
-        <v>253.289003284719</v>
+        <v>253.28900328471937</v>
       </c>
       <c r="D68" s="4">
         <f t="shared" si="22"/>
-        <v>260.791849669523</v>
+        <v>260.79184966952323</v>
       </c>
       <c r="E68" s="4">
         <f t="shared" si="23"/>
-        <v>252.495352330411</v>
+        <v>252.49535233041098</v>
       </c>
       <c r="F68" s="4">
         <f t="shared" si="24"/>
-        <v>261.585500623832</v>
+        <v>261.58550062383159</v>
       </c>
       <c r="G68" s="4">
         <f t="shared" si="25"/>
-        <v>250.813291378863</v>
+        <v>250.81329137886325</v>
       </c>
       <c r="H68" s="4">
         <f t="shared" si="26"/>
-        <v>263.267561575379</v>
+        <v>263.26756157537932</v>
       </c>
     </row>
     <row r="69" spans="1:8">
@@ -8420,31 +7872,31 @@
       </c>
       <c r="B69" s="4">
         <f t="shared" si="20"/>
-        <v>265.119058196357</v>
+        <v>265.11905819635717</v>
       </c>
       <c r="C69" s="4">
         <f t="shared" si="21"/>
-        <v>260.563248344446</v>
+        <v>260.56324834444638</v>
       </c>
       <c r="D69" s="4">
         <f t="shared" si="22"/>
-        <v>269.674868048268</v>
+        <v>269.67486804826797</v>
       </c>
       <c r="E69" s="4">
         <f t="shared" si="23"/>
-        <v>259.599421377673</v>
+        <v>259.59942137767291</v>
       </c>
       <c r="F69" s="4">
         <f t="shared" si="24"/>
-        <v>270.638695015041</v>
+        <v>270.63869501504143</v>
       </c>
       <c r="G69" s="4">
         <f t="shared" si="25"/>
-        <v>257.556690003058</v>
+        <v>257.55669000305846</v>
       </c>
       <c r="H69" s="4">
         <f t="shared" si="26"/>
-        <v>272.681426389656</v>
+        <v>272.68142638965588</v>
       </c>
     </row>
     <row r="70" spans="1:8">
@@ -8453,31 +7905,31 @@
       </c>
       <c r="B70" s="4">
         <f t="shared" si="20"/>
-        <v>273.197689915593</v>
+        <v>273.19768991559306</v>
       </c>
       <c r="C70" s="4">
         <f t="shared" si="21"/>
-        <v>267.586320594641</v>
+        <v>267.58632059464117</v>
       </c>
       <c r="D70" s="4">
         <f t="shared" si="22"/>
-        <v>278.809059236545</v>
+        <v>278.80905923654495</v>
       </c>
       <c r="E70" s="4">
         <f t="shared" si="23"/>
-        <v>266.399179504942</v>
+        <v>266.39917950494214</v>
       </c>
       <c r="F70" s="4">
         <f t="shared" si="24"/>
-        <v>279.996200326244</v>
+        <v>279.99620032624398</v>
       </c>
       <c r="G70" s="4">
         <f t="shared" si="25"/>
-        <v>263.883156988847</v>
+        <v>263.88315698884662</v>
       </c>
       <c r="H70" s="4">
         <f t="shared" si="26"/>
-        <v>282.512222842339</v>
+        <v>282.5122228423395</v>
       </c>
     </row>
     <row r="71" spans="1:8">
@@ -8486,68 +7938,59 @@
       </c>
       <c r="B71" s="4">
         <f t="shared" si="20"/>
-        <v>281.276321634829</v>
+        <v>281.27632163482895</v>
       </c>
       <c r="C71" s="4">
         <f t="shared" si="21"/>
-        <v>274.474162954193</v>
+        <v>274.4741629541931</v>
       </c>
       <c r="D71" s="4">
         <f t="shared" si="22"/>
-        <v>288.078480315465</v>
+        <v>288.07848031546479</v>
       </c>
       <c r="E71" s="4">
         <f t="shared" si="23"/>
-        <v>273.035098510817</v>
+        <v>273.03509851081657</v>
       </c>
       <c r="F71" s="4">
         <f t="shared" si="24"/>
-        <v>289.517544758841</v>
+        <v>289.51754475884132</v>
       </c>
       <c r="G71" s="4">
         <f t="shared" si="25"/>
-        <v>269.985150553438</v>
+        <v>269.98515055343796</v>
       </c>
       <c r="H71" s="4">
         <f t="shared" si="26"/>
-        <v>292.56749271622</v>
+        <v>292.56749271621993</v>
       </c>
     </row>
-    <row r="106" ht="16" customHeight="1" spans="1:5">
-      <c r="A106" s="10" t="s">
+    <row r="106" spans="1:5" ht="16" customHeight="1">
+      <c r="A106" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="B106" s="10"/>
-      <c r="C106" s="10"/>
-      <c r="D106" s="10"/>
-      <c r="E106" s="10"/>
+      <c r="B106" s="11"/>
+      <c r="C106" s="11"/>
+      <c r="D106" s="11"/>
+      <c r="E106" s="11"/>
     </row>
     <row r="107" spans="1:5">
-      <c r="A107" s="10"/>
-      <c r="B107" s="10"/>
-      <c r="C107" s="10"/>
-      <c r="D107" s="10"/>
-      <c r="E107" s="10"/>
+      <c r="A107" s="11"/>
+      <c r="B107" s="11"/>
+      <c r="C107" s="11"/>
+      <c r="D107" s="11"/>
+      <c r="E107" s="11"/>
     </row>
     <row r="108" spans="1:5">
-      <c r="A108" s="10"/>
-      <c r="B108" s="10"/>
-      <c r="C108" s="10"/>
-      <c r="D108" s="10"/>
-      <c r="E108" s="10"/>
+      <c r="A108" s="11"/>
+      <c r="B108" s="11"/>
+      <c r="C108" s="11"/>
+      <c r="D108" s="11"/>
+      <c r="E108" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="C47:E47"/>
-    <mergeCell ref="C61:H61"/>
-    <mergeCell ref="C62:D62"/>
-    <mergeCell ref="E62:F62"/>
-    <mergeCell ref="G62:H62"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="A42:A43"/>
-    <mergeCell ref="A44:A45"/>
-    <mergeCell ref="A51:A52"/>
-    <mergeCell ref="A53:A54"/>
+    <mergeCell ref="A106:E108"/>
     <mergeCell ref="A55:A56"/>
     <mergeCell ref="B51:B52"/>
     <mergeCell ref="B53:B54"/>
@@ -8555,10 +7998,18 @@
     <mergeCell ref="C51:C52"/>
     <mergeCell ref="C53:C54"/>
     <mergeCell ref="C55:C56"/>
-    <mergeCell ref="A106:E108"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="A42:A43"/>
+    <mergeCell ref="A44:A45"/>
+    <mergeCell ref="A51:A52"/>
+    <mergeCell ref="A53:A54"/>
+    <mergeCell ref="C47:E47"/>
+    <mergeCell ref="C61:H61"/>
+    <mergeCell ref="C62:D62"/>
+    <mergeCell ref="E62:F62"/>
+    <mergeCell ref="G62:H62"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
   <ignoredErrors>
     <ignoredError sqref="K25 K23 E23 G2:G21" formula="1"/>
   </ignoredErrors>

--- a/7 semester/SMAD/lab3/Vanus/lab3.xlsx
+++ b/7 semester/SMAD/lab3/Vanus/lab3.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sasha\BSUIR\7 semester\SMAD\lab3\Vanus\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB45930F-F610-45A9-8ECC-9EF760A7946F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6B35A27-06EB-4085-B0EA-3BE23C4B441C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="46665" yWindow="1110" windowWidth="28800" windowHeight="16545" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9" yWindow="9" windowWidth="21925" windowHeight="12977" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -263,6 +263,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -271,9 +274,6 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -7216,8 +7216,8 @@
         <f t="shared" si="10"/>
         <v>8709.75</v>
       </c>
-      <c r="I23" s="2">
-        <f t="shared" si="10"/>
+      <c r="I23" s="4">
+        <f>SUM(I2:I21)</f>
         <v>909.25</v>
       </c>
       <c r="J23" s="2">
@@ -7304,8 +7304,8 @@
         <f t="shared" si="12"/>
         <v>435.48750000000001</v>
       </c>
-      <c r="I25" s="2">
-        <f t="shared" si="12"/>
+      <c r="I25" s="4">
+        <f>AVERAGE(I2:I21)</f>
         <v>45.462499999999999</v>
       </c>
       <c r="J25" s="2">
@@ -7456,7 +7456,7 @@
       </c>
     </row>
     <row r="40" spans="1:5">
-      <c r="A40" s="8">
+      <c r="A40" s="9">
         <v>0.9</v>
       </c>
       <c r="B40" s="2" t="s">
@@ -7472,7 +7472,7 @@
       </c>
     </row>
     <row r="41" spans="1:5">
-      <c r="A41" s="8"/>
+      <c r="A41" s="9"/>
       <c r="B41" s="2" t="s">
         <v>28</v>
       </c>
@@ -7486,7 +7486,7 @@
       </c>
     </row>
     <row r="42" spans="1:5">
-      <c r="A42" s="8">
+      <c r="A42" s="9">
         <v>0.95</v>
       </c>
       <c r="B42" s="2" t="s">
@@ -7502,7 +7502,7 @@
       </c>
     </row>
     <row r="43" spans="1:5">
-      <c r="A43" s="8"/>
+      <c r="A43" s="9"/>
       <c r="B43" s="2" t="s">
         <v>28</v>
       </c>
@@ -7516,7 +7516,7 @@
       </c>
     </row>
     <row r="44" spans="1:5">
-      <c r="A44" s="8">
+      <c r="A44" s="9">
         <v>0.99</v>
       </c>
       <c r="B44" s="2" t="s">
@@ -7532,7 +7532,7 @@
       </c>
     </row>
     <row r="45" spans="1:5">
-      <c r="A45" s="8"/>
+      <c r="A45" s="9"/>
       <c r="B45" s="2" t="s">
         <v>28</v>
       </c>
@@ -7549,11 +7549,11 @@
       <c r="A47" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C47" s="8" t="s">
+      <c r="C47" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="D47" s="8"/>
-      <c r="E47" s="8"/>
+      <c r="D47" s="9"/>
+      <c r="E47" s="9"/>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
@@ -7573,58 +7573,58 @@
       </c>
     </row>
     <row r="51" spans="1:8" ht="17.05" customHeight="1">
-      <c r="A51" s="8">
+      <c r="A51" s="9">
         <v>0.9</v>
       </c>
-      <c r="B51" s="9">
+      <c r="B51" s="10">
         <f>FINV(1-A51,2,$A$23-2)</f>
         <v>2.6239469851339554</v>
       </c>
-      <c r="C51" s="8" t="str">
+      <c r="C51" s="9" t="str">
         <f>IF($B$58&gt;B51,"значимый","не значимый")</f>
         <v>значимый</v>
       </c>
     </row>
     <row r="52" spans="1:8">
-      <c r="A52" s="8"/>
-      <c r="B52" s="10"/>
-      <c r="C52" s="8"/>
+      <c r="A52" s="9"/>
+      <c r="B52" s="11"/>
+      <c r="C52" s="9"/>
     </row>
     <row r="53" spans="1:8" ht="16" customHeight="1">
-      <c r="A53" s="8">
+      <c r="A53" s="9">
         <v>0.95</v>
       </c>
-      <c r="B53" s="9">
+      <c r="B53" s="10">
         <f t="shared" ref="B53" si="16">FINV(1-A53,2,$A$23-2)</f>
         <v>3.5545571456617857</v>
       </c>
-      <c r="C53" s="8" t="str">
+      <c r="C53" s="9" t="str">
         <f t="shared" ref="C53" si="17">IF($B$58&gt;B53,"значимый","не значимый")</f>
         <v>значимый</v>
       </c>
     </row>
     <row r="54" spans="1:8">
-      <c r="A54" s="8"/>
-      <c r="B54" s="10"/>
-      <c r="C54" s="8"/>
+      <c r="A54" s="9"/>
+      <c r="B54" s="11"/>
+      <c r="C54" s="9"/>
     </row>
     <row r="55" spans="1:8" ht="16" customHeight="1">
-      <c r="A55" s="8">
+      <c r="A55" s="9">
         <v>0.99</v>
       </c>
-      <c r="B55" s="9">
+      <c r="B55" s="10">
         <f t="shared" ref="B55" si="18">FINV(1-A55,2,$A$23-2)</f>
         <v>6.0129048348005281</v>
       </c>
-      <c r="C55" s="8" t="str">
+      <c r="C55" s="9" t="str">
         <f t="shared" ref="C55" si="19">IF($B$58&gt;B55,"значимый","не значимый")</f>
         <v>значимый</v>
       </c>
     </row>
     <row r="56" spans="1:8">
-      <c r="A56" s="8"/>
-      <c r="B56" s="10"/>
-      <c r="C56" s="8"/>
+      <c r="A56" s="9"/>
+      <c r="B56" s="11"/>
+      <c r="C56" s="9"/>
     </row>
     <row r="57" spans="1:8">
       <c r="B57" s="6"/>
@@ -7639,14 +7639,14 @@
       </c>
     </row>
     <row r="61" spans="1:8" ht="16" customHeight="1">
-      <c r="C61" s="8" t="s">
+      <c r="C61" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D61" s="8"/>
-      <c r="E61" s="8"/>
-      <c r="F61" s="8"/>
-      <c r="G61" s="8"/>
-      <c r="H61" s="8"/>
+      <c r="D61" s="9"/>
+      <c r="E61" s="9"/>
+      <c r="F61" s="9"/>
+      <c r="G61" s="9"/>
+      <c r="H61" s="9"/>
     </row>
     <row r="62" spans="1:8">
       <c r="A62" s="2" t="s">
@@ -7655,18 +7655,18 @@
       <c r="B62" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C62" s="8">
+      <c r="C62" s="9">
         <v>0.9</v>
       </c>
-      <c r="D62" s="8"/>
-      <c r="E62" s="8">
+      <c r="D62" s="9"/>
+      <c r="E62" s="9">
         <v>0.95</v>
       </c>
-      <c r="F62" s="8"/>
-      <c r="G62" s="8">
+      <c r="F62" s="9"/>
+      <c r="G62" s="9">
         <v>0.99</v>
       </c>
-      <c r="H62" s="8"/>
+      <c r="H62" s="9"/>
     </row>
     <row r="63" spans="1:8">
       <c r="A63" s="2">
@@ -7966,30 +7966,40 @@
       </c>
     </row>
     <row r="106" spans="1:5" ht="16" customHeight="1">
-      <c r="A106" s="11" t="s">
+      <c r="A106" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="B106" s="11"/>
-      <c r="C106" s="11"/>
-      <c r="D106" s="11"/>
-      <c r="E106" s="11"/>
+      <c r="B106" s="8"/>
+      <c r="C106" s="8"/>
+      <c r="D106" s="8"/>
+      <c r="E106" s="8"/>
     </row>
     <row r="107" spans="1:5">
-      <c r="A107" s="11"/>
-      <c r="B107" s="11"/>
-      <c r="C107" s="11"/>
-      <c r="D107" s="11"/>
-      <c r="E107" s="11"/>
+      <c r="A107" s="8"/>
+      <c r="B107" s="8"/>
+      <c r="C107" s="8"/>
+      <c r="D107" s="8"/>
+      <c r="E107" s="8"/>
     </row>
     <row r="108" spans="1:5">
-      <c r="A108" s="11"/>
-      <c r="B108" s="11"/>
-      <c r="C108" s="11"/>
-      <c r="D108" s="11"/>
-      <c r="E108" s="11"/>
+      <c r="A108" s="8"/>
+      <c r="B108" s="8"/>
+      <c r="C108" s="8"/>
+      <c r="D108" s="8"/>
+      <c r="E108" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="C47:E47"/>
+    <mergeCell ref="C61:H61"/>
+    <mergeCell ref="C62:D62"/>
+    <mergeCell ref="E62:F62"/>
+    <mergeCell ref="G62:H62"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="A42:A43"/>
+    <mergeCell ref="A44:A45"/>
+    <mergeCell ref="A51:A52"/>
+    <mergeCell ref="A53:A54"/>
     <mergeCell ref="A106:E108"/>
     <mergeCell ref="A55:A56"/>
     <mergeCell ref="B51:B52"/>
@@ -7998,16 +8008,6 @@
     <mergeCell ref="C51:C52"/>
     <mergeCell ref="C53:C54"/>
     <mergeCell ref="C55:C56"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="A42:A43"/>
-    <mergeCell ref="A44:A45"/>
-    <mergeCell ref="A51:A52"/>
-    <mergeCell ref="A53:A54"/>
-    <mergeCell ref="C47:E47"/>
-    <mergeCell ref="C61:H61"/>
-    <mergeCell ref="C62:D62"/>
-    <mergeCell ref="E62:F62"/>
-    <mergeCell ref="G62:H62"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
